--- a/5/search/FY5_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
+++ b/5/search/FY5_Missile2_results/fine_tuned/top10_fine_tuned_solutions.xlsx
@@ -492,34 +492,34 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B2" t="n">
-        <v>133.9</v>
+        <v>138.4</v>
       </c>
       <c r="C2" t="n">
         <v>19.4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="E2" t="n">
-        <v>11724.79895538409</v>
+        <v>11714.73150910379</v>
       </c>
       <c r="F2" t="n">
-        <v>263.1172685944716</v>
+        <v>357.3491697051104</v>
       </c>
       <c r="G2" t="n">
         <v>1300</v>
       </c>
       <c r="H2" t="n">
-        <v>11659.06694277503</v>
+        <v>11701.48131847599</v>
       </c>
       <c r="I2" t="n">
-        <v>379.772797903465</v>
+        <v>381.6517384649568</v>
       </c>
       <c r="J2" t="n">
-        <v>1295.1</v>
+        <v>1299.804</v>
       </c>
       <c r="K2" t="n">
         <v>3.600000000000001</v>
@@ -530,37 +530,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119.4</v>
+        <v>121.8</v>
       </c>
       <c r="B3" t="n">
-        <v>133.9</v>
+        <v>134.4</v>
       </c>
       <c r="C3" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6000000000000001</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>11698.50615034047</v>
+        <v>11668.53025240263</v>
       </c>
       <c r="F3" t="n">
-        <v>309.7794803180691</v>
+        <v>147.4408652237689</v>
       </c>
       <c r="G3" t="n">
         <v>1300</v>
       </c>
       <c r="H3" t="n">
-        <v>11659.06694277503</v>
+        <v>11526.88453457313</v>
       </c>
       <c r="I3" t="n">
-        <v>379.7727979034653</v>
+        <v>375.8920210986379</v>
       </c>
       <c r="J3" t="n">
-        <v>1298.236</v>
+        <v>1280.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.399999999999999</v>
+        <v>3.599999999999998</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -568,37 +568,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117.8</v>
+        <v>118.6</v>
       </c>
       <c r="B4" t="n">
-        <v>131.9</v>
+        <v>135.4</v>
       </c>
       <c r="C4" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>11757.3687632112</v>
+        <v>11703.70244869684</v>
       </c>
       <c r="F4" t="n">
-        <v>356.8598587435654</v>
+        <v>377.5778974589712</v>
       </c>
       <c r="G4" t="n">
         <v>1300</v>
       </c>
       <c r="H4" t="n">
-        <v>11745.06548363903</v>
+        <v>11703.70244869684</v>
       </c>
       <c r="I4" t="n">
-        <v>380.1951048697392</v>
+        <v>377.5778974589712</v>
       </c>
       <c r="J4" t="n">
-        <v>1299.804</v>
+        <v>1300</v>
       </c>
       <c r="K4" t="n">
-        <v>3.300000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -606,37 +606,37 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119.4</v>
+        <v>120.2</v>
       </c>
       <c r="B5" t="n">
-        <v>133.9</v>
+        <v>136.4</v>
       </c>
       <c r="C5" t="n">
-        <v>20.2</v>
+        <v>18.8</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2</v>
+        <v>1.4</v>
       </c>
       <c r="E5" t="n">
-        <v>11672.21334529684</v>
+        <v>11710.09589045716</v>
       </c>
       <c r="F5" t="n">
-        <v>356.4416920416661</v>
+        <v>216.277160145924</v>
       </c>
       <c r="G5" t="n">
         <v>1300</v>
       </c>
       <c r="H5" t="n">
-        <v>11659.06694277503</v>
+        <v>11614.03920144865</v>
       </c>
       <c r="I5" t="n">
-        <v>379.7727979034647</v>
+        <v>381.3190763270032</v>
       </c>
       <c r="J5" t="n">
-        <v>1299.804</v>
+        <v>1290.396</v>
       </c>
       <c r="K5" t="n">
-        <v>3.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -644,37 +644,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119.4</v>
+        <v>121.8</v>
       </c>
       <c r="B6" t="n">
-        <v>134.9</v>
+        <v>138.4</v>
       </c>
       <c r="C6" t="n">
-        <v>19.4</v>
+        <v>18.2</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>11715.27542256396</v>
+        <v>11672.66158583933</v>
       </c>
       <c r="F6" t="n">
-        <v>280.0188165302029</v>
+        <v>140.7777065107516</v>
       </c>
       <c r="G6" t="n">
         <v>1300</v>
       </c>
       <c r="H6" t="n">
-        <v>11662.29708947381</v>
+        <v>11526.80022164585</v>
       </c>
       <c r="I6" t="n">
-        <v>374.0402110262938</v>
+        <v>376.0280039295155</v>
       </c>
       <c r="J6" t="n">
-        <v>1296.864</v>
+        <v>1280.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.100000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -682,37 +682,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117.8</v>
+        <v>120.2</v>
       </c>
       <c r="B7" t="n">
-        <v>135.9</v>
+        <v>137.4</v>
       </c>
       <c r="C7" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="E7" t="n">
-        <v>11745.03750044061</v>
+        <v>11700.63911546051</v>
       </c>
       <c r="F7" t="n">
-        <v>380.2481797282526</v>
+        <v>232.5255264226539</v>
       </c>
       <c r="G7" t="n">
         <v>1300</v>
       </c>
       <c r="H7" t="n">
-        <v>11745.03750044061</v>
+        <v>11617.70118666012</v>
       </c>
       <c r="I7" t="n">
-        <v>380.2481797282526</v>
+        <v>375.0271557687806</v>
       </c>
       <c r="J7" t="n">
-        <v>1300</v>
+        <v>1292.944</v>
       </c>
       <c r="K7" t="n">
-        <v>3.100000000000001</v>
+        <v>3.5</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -720,37 +720,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B8" t="n">
-        <v>136.9</v>
+        <v>135.4</v>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>11723.11024647166</v>
+        <v>11742.59137523593</v>
       </c>
       <c r="F8" t="n">
-        <v>266.114244104725</v>
+        <v>306.2505605352021</v>
       </c>
       <c r="G8" t="n">
         <v>1300</v>
       </c>
       <c r="H8" t="n">
-        <v>11655.90552260174</v>
+        <v>11703.70244869684</v>
       </c>
       <c r="I8" t="n">
-        <v>385.3834148470789</v>
+        <v>377.5778974589714</v>
       </c>
       <c r="J8" t="n">
-        <v>1295.1</v>
+        <v>1298.236</v>
       </c>
       <c r="K8" t="n">
-        <v>3.100000000000001</v>
+        <v>3.400000000000002</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -758,37 +758,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117.8</v>
+        <v>118.6</v>
       </c>
       <c r="B9" t="n">
-        <v>131.9</v>
+        <v>138.4</v>
       </c>
       <c r="C9" t="n">
-        <v>19.8</v>
+        <v>18.8</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6000000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="E9" t="n">
-        <v>11781.97532235553</v>
+        <v>11754.48208098718</v>
       </c>
       <c r="F9" t="n">
-        <v>310.1893664912177</v>
+        <v>284.4414634255713</v>
       </c>
       <c r="G9" t="n">
         <v>1300</v>
       </c>
       <c r="H9" t="n">
-        <v>11745.06548363903</v>
+        <v>11701.48131847599</v>
       </c>
       <c r="I9" t="n">
-        <v>380.1951048697396</v>
+        <v>381.6517384649574</v>
       </c>
       <c r="J9" t="n">
-        <v>1298.236</v>
+        <v>1296.864</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -796,37 +796,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119.4</v>
+        <v>118.6</v>
       </c>
       <c r="B10" t="n">
-        <v>136.9</v>
+        <v>131.4</v>
       </c>
       <c r="C10" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
         <v>0.6000000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>11696.22835692369</v>
+        <v>11741.99779733209</v>
       </c>
       <c r="F10" t="n">
-        <v>313.8219124016664</v>
+        <v>307.339259424733</v>
       </c>
       <c r="G10" t="n">
         <v>1300</v>
       </c>
       <c r="H10" t="n">
-        <v>11655.90552260174</v>
+        <v>11704.25773125205</v>
       </c>
       <c r="I10" t="n">
-        <v>385.3834148470789</v>
+        <v>376.5594372074751</v>
       </c>
       <c r="J10" t="n">
         <v>1298.236</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>3.399999999999999</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -834,37 +834,37 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119.4</v>
+        <v>121.8</v>
       </c>
       <c r="B11" t="n">
-        <v>134.9</v>
+        <v>130.4</v>
       </c>
       <c r="C11" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>11688.78625601889</v>
+        <v>11666.92830678432</v>
       </c>
       <c r="F11" t="n">
-        <v>327.0295137782487</v>
+        <v>150.0245390104487</v>
       </c>
       <c r="G11" t="n">
         <v>1300</v>
       </c>
       <c r="H11" t="n">
-        <v>11662.29708947381</v>
+        <v>11529.49823531879</v>
       </c>
       <c r="I11" t="n">
-        <v>374.0402110262939</v>
+        <v>371.6765533414228</v>
       </c>
       <c r="J11" t="n">
-        <v>1299.216</v>
+        <v>1280.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.900000000000002</v>
+        <v>3.300000000000001</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
